--- a/Configs/Datas/ZZZ.CharacterAttribute.xlsx
+++ b/Configs/Datas/ZZZ.CharacterAttribute.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81202E8A-22C1-48DD-B25E-7F4860E86832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE7922F-FF4F-4873-BDD7-C5E592152F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="627" activeTab="3" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="5700" yWindow="3210" windowWidth="21600" windowHeight="11385" tabRatio="627" activeTab="2" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="99">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -366,6 +366,10 @@
   </si>
   <si>
     <t>基础抗打断等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -748,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="15.875" customWidth="1"/>
@@ -1089,6 +1093,56 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8">
+        <v>12000</v>
+      </c>
+      <c r="G8">
+        <v>250</v>
+      </c>
+      <c r="H8">
+        <v>850</v>
+      </c>
+      <c r="I8">
+        <v>18.5</v>
+      </c>
+      <c r="J8">
+        <v>600</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>110</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>1.5</v>
+      </c>
+      <c r="O8">
+        <v>0.05</v>
+      </c>
+      <c r="P8">
+        <v>0.5</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1097,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFA8F43-2EBF-4BCF-95FD-D9F494F3D758}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="15.375" customWidth="1"/>
@@ -1267,6 +1321,29 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8">
+        <v>120</v>
+      </c>
+      <c r="E8">
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <v>1.2</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1275,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63FB7DDE-BB86-40B6-840A-691401D44A36}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17" customWidth="1"/>
@@ -1595,6 +1672,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1603,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72483E5-14A8-4FA8-A15B-52739B7BA6E5}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="16" customWidth="1"/>
@@ -1711,6 +1829,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/Datas/ZZZ.CharacterAttribute.xlsx
+++ b/Configs/Datas/ZZZ.CharacterAttribute.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE7922F-FF4F-4873-BDD7-C5E592152F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F06D9F9-63A6-451A-8AC2-64FB8872C193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="3210" windowWidth="21600" windowHeight="11385" tabRatio="627" activeTab="2" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="627" activeTab="3" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
